--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,27 +618,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>45979.45833333334</v>
+        <v>45979.375</v>
       </c>
     </row>
     <row r="3">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45979.75</v>
+        <v>45979.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -856,116 +856,235 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>45979.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Chile Primera B</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Rangers</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>San Marcos</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>45979.85416666666</v>
       </c>
     </row>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45979.45833333334</v>
+        <v>45979.75</v>
       </c>
     </row>
     <row r="4">
@@ -856,7 +856,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,125 +966,6 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45979.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>45979</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="3" t="n">
         <v>45979.85416666666</v>
       </c>
     </row>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
         <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>3.92</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="N3" t="n">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="M4" t="n">
         <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3.63</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
         <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="M3" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="N4" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>2.39</v>
       </c>
       <c r="N2" t="n">
-        <v>2.03</v>
+        <v>3.34</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,76 +778,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>3.63</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45979.75</v>
+        <v>45979.625</v>
       </c>
     </row>
     <row r="4">
@@ -856,116 +856,235 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>45979.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Chile Primera B</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Rangers</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>San Marcos</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L5" t="n">
         <v>1.8</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M5" t="n">
         <v>3.25</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N5" t="n">
         <v>3.92</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AB5" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>45979.85416666666</v>
       </c>
     </row>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.57</v>
+        <v>3.3</v>
       </c>
       <c r="M2" t="n">
-        <v>2.39</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.34</v>
+        <v>2.03</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45979.375</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
         <v>2.75</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1064,7 +1064,7 @@
         <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
         <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="O2" t="n">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T2" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
         <v>7.3</v>
@@ -695,37 +695,37 @@
         <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AG2" t="n">
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45979.375</v>
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,76 +778,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>8.300000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45979.625</v>
+        <v>45979.75</v>
       </c>
     </row>
     <row r="4">
@@ -856,7 +856,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -966,125 +966,6 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45979.75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>45979</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="3" t="n">
         <v>45979.85416666666</v>
       </c>
     </row>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,10 +668,10 @@
         <v>2.07</v>
       </c>
       <c r="O2" t="n">
-        <v>4.23</v>
+        <v>4.05</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
         <v>2.7</v>
@@ -689,10 +689,10 @@
         <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.04</v>
@@ -716,7 +716,7 @@
         <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF2" t="n">
         <v>1.88</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="O3" t="n">
         <v>2.75</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="O4" t="n">
         <v>2.3</v>
@@ -945,7 +945,7 @@
         <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -966,6 +966,125 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
+        <v>45979.85416666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>45979.85416666666</v>
       </c>
     </row>

--- a/jogos_2025-11-18.xlsx
+++ b/jogos_2025-11-18.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -642,93 +642,93 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N2" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T2" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V2" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X2" t="n">
         <v>1.07</v>
       </c>
-      <c r="X2" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>45979.375</v>
+        <v>45979.54166666666</v>
       </c>
     </row>
     <row r="3">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="N4" t="n">
-        <v>3.92</v>
+        <v>12.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45979.85416666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>3.92</v>
       </c>
       <c r="O5" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45979.85416666666</v>
